--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OHIO_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OHIO_2018.xlsx
@@ -1039,7 +1039,7 @@
         <v>4</v>
       </c>
       <c r="D38">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="D62">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="63">
@@ -2425,7 +2425,7 @@
         <v>4</v>
       </c>
       <c r="D115">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="116">
@@ -2731,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="D132">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="133">
@@ -2983,7 +2983,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="147">
@@ -3415,7 +3415,7 @@
         <v>4</v>
       </c>
       <c r="D170">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="171">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C192">
@@ -4009,7 +4009,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="204">
@@ -4297,7 +4297,7 @@
         <v>4</v>
       </c>
       <c r="D219">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="220">
@@ -4603,7 +4603,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="237">
@@ -4639,7 +4639,7 @@
         <v>4</v>
       </c>
       <c r="D238">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="239">
@@ -4819,7 +4819,7 @@
         <v>4</v>
       </c>
       <c r="D248">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="249">
@@ -4945,7 +4945,7 @@
         <v>4</v>
       </c>
       <c r="D255">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="256">
@@ -4981,7 +4981,7 @@
         <v>4</v>
       </c>
       <c r="D257">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="258">
@@ -5125,7 +5125,7 @@
         <v>4</v>
       </c>
       <c r="D265">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="266">
@@ -5287,7 +5287,7 @@
         <v>4</v>
       </c>
       <c r="D274">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="275">
@@ -5305,7 +5305,7 @@
         <v>4</v>
       </c>
       <c r="D275">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="276">
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="D281">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="282">
@@ -5467,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="D284">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="285">
@@ -6619,7 +6619,7 @@
         <v>4</v>
       </c>
       <c r="D348">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="349">
@@ -6889,7 +6889,7 @@
         <v>4</v>
       </c>
       <c r="D363">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="364">
@@ -6907,7 +6907,7 @@
         <v>4</v>
       </c>
       <c r="D364">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="365">
@@ -6961,7 +6961,7 @@
         <v>4</v>
       </c>
       <c r="D367">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="368">
@@ -6997,7 +6997,7 @@
         <v>4</v>
       </c>
       <c r="D369">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="370">
@@ -7069,7 +7069,7 @@
         <v>4</v>
       </c>
       <c r="D373">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="374">
@@ -7321,7 +7321,7 @@
         <v>4</v>
       </c>
       <c r="D387">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="388">
@@ -7717,7 +7717,7 @@
         <v>4</v>
       </c>
       <c r="D409">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="410">
@@ -7753,7 +7753,7 @@
         <v>4</v>
       </c>
       <c r="D411">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="412">
@@ -7879,7 +7879,7 @@
         <v>4</v>
       </c>
       <c r="D418">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="419">
@@ -7915,7 +7915,7 @@
         <v>4</v>
       </c>
       <c r="D420">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="421">
@@ -8023,7 +8023,7 @@
         <v>4</v>
       </c>
       <c r="D426">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="427">
@@ -8077,7 +8077,7 @@
         <v>4</v>
       </c>
       <c r="D429">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="430">
@@ -8257,7 +8257,7 @@
         <v>4</v>
       </c>
       <c r="D439">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="440">
@@ -8293,7 +8293,7 @@
         <v>4</v>
       </c>
       <c r="D441">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="442">
@@ -8563,7 +8563,7 @@
         <v>4</v>
       </c>
       <c r="D456">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="457">
@@ -8779,7 +8779,7 @@
         <v>4</v>
       </c>
       <c r="D468">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="469">
@@ -8815,7 +8815,7 @@
         <v>4</v>
       </c>
       <c r="D470">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="471">
@@ -8905,7 +8905,7 @@
         <v>4</v>
       </c>
       <c r="D475">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="476">
@@ -9229,7 +9229,7 @@
         <v>4</v>
       </c>
       <c r="D493">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="494">
@@ -9499,7 +9499,7 @@
         <v>4</v>
       </c>
       <c r="D508">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="509">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C516">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C546">
@@ -10543,7 +10543,7 @@
         <v>4</v>
       </c>
       <c r="D566">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="567">
@@ -10615,7 +10615,7 @@
         <v>4</v>
       </c>
       <c r="D570">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="571">
@@ -11209,7 +11209,7 @@
         <v>4</v>
       </c>
       <c r="D603">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="604">
@@ -11641,7 +11641,7 @@
         <v>4</v>
       </c>
       <c r="D627">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="628">
@@ -12505,7 +12505,7 @@
         <v>4</v>
       </c>
       <c r="D675">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="676">
@@ -12937,7 +12937,7 @@
         <v>4</v>
       </c>
       <c r="D699">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="700">
@@ -13153,7 +13153,7 @@
         <v>4</v>
       </c>
       <c r="D711">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="712">
@@ -13207,7 +13207,7 @@
         <v>4</v>
       </c>
       <c r="D714">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="715">
@@ -14467,7 +14467,7 @@
         <v>4</v>
       </c>
       <c r="D784">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="785">
@@ -14611,7 +14611,7 @@
         <v>4</v>
       </c>
       <c r="D792">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="793">
@@ -14809,7 +14809,7 @@
         <v>4</v>
       </c>
       <c r="D803">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="804">
@@ -14863,7 +14863,7 @@
         <v>4</v>
       </c>
       <c r="D806">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="807">
@@ -14989,7 +14989,7 @@
         <v>4</v>
       </c>
       <c r="D813">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="814">
@@ -15097,7 +15097,7 @@
         <v>4</v>
       </c>
       <c r="D819">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="820">
@@ -15187,7 +15187,7 @@
         <v>4</v>
       </c>
       <c r="D824">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="825">
@@ -15709,7 +15709,7 @@
         <v>4</v>
       </c>
       <c r="D853">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="854">
@@ -16105,7 +16105,7 @@
         <v>4</v>
       </c>
       <c r="D875">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
   </sheetData>
